--- a/Análisis programas postgrado SNIES/Nuevos posgrado.xlsx
+++ b/Análisis programas postgrado SNIES/Nuevos posgrado.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,22 +16,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -50,23 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,117 +421,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>CÓDIGO_INSTITUCIÓN</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>NOMBRE_INSTITUCIÓN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SECTOR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO_OFERTA_PROGRAMA</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>MUNICIPIO_OFERTA_PROGRAMA</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>CÓDIGO_SNIES_DEL_PROGRAMA</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>NOMBRE_DEL_PROGRAMA</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>MODALIDAD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>NÚMERO_CRÉDITOS</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>NÚMERO_PERIODOS_DE_DURACIÓN</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PERIODICIDAD</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>COSTO_MATRÍCULA_ESTUD_NUEVOS</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>PERIODICIDAD_ADMISIONES</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>FECHA_DE_REGISTRO_EN_SNIES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_AMPLIO</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_ESPECÍFIC</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_DETALLADO</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>NÚCLEO_BÁSICO_DEL_CONOCIMIENTO</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>NIVEL_DE_FORMACIÓN</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PROGINSTI</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>FECHA_OBTENCION</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>DIVISIÓN UNINORTE</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -606,7 +591,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="O2" t="inlineStr">
@@ -709,7 +694,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="O3" t="inlineStr">
@@ -812,7 +797,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="O4" t="inlineStr">
@@ -915,7 +900,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>45791</v>
       </c>
       <c r="O5" t="inlineStr">
@@ -1018,7 +1003,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>45791</v>
       </c>
       <c r="O6" t="inlineStr">
@@ -1121,7 +1106,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>45763</v>
       </c>
       <c r="O7" t="inlineStr">
@@ -1224,7 +1209,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N8" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="O8" t="inlineStr">
@@ -1327,7 +1312,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="N9" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="O9" t="inlineStr">
@@ -1430,7 +1415,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="N10" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="O10" t="inlineStr">
@@ -1480,10 +1465,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1105</t>
-        </is>
+      <c r="A11" t="n">
+        <v>1105</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1537,7 +1520,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N11" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O11" t="inlineStr">
@@ -1583,10 +1566,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
+      <c r="A12" t="n">
+        <v>1112</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1640,7 +1621,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" s="1" t="n">
         <v>39799</v>
       </c>
       <c r="O12" t="inlineStr">
@@ -1686,10 +1667,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
+      <c r="A13" t="n">
+        <v>1117</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1741,7 +1720,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="N13" s="1" t="n">
         <v>40407</v>
       </c>
       <c r="O13" t="inlineStr">
@@ -1787,10 +1766,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
+      <c r="A14" t="n">
+        <v>1201</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1844,7 +1821,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" s="1" t="n">
         <v>42537</v>
       </c>
       <c r="O14" t="inlineStr">
@@ -1890,10 +1867,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A15" t="n">
+        <v>1203</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1945,7 +1920,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="N15" s="1" t="n">
         <v>36416</v>
       </c>
       <c r="O15" t="inlineStr">
@@ -1991,10 +1966,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
+      <c r="A16" t="n">
+        <v>1204</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2048,7 +2021,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="N16" s="1" t="n">
         <v>42770</v>
       </c>
       <c r="O16" t="inlineStr">
@@ -2094,10 +2067,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1208</t>
-        </is>
+      <c r="A17" t="n">
+        <v>1208</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2149,7 +2120,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="N17" s="1" t="n">
         <v>42211</v>
       </c>
       <c r="O17" t="inlineStr">
@@ -2195,10 +2166,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1214</t>
-        </is>
+      <c r="A18" t="n">
+        <v>1214</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2250,7 +2219,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N18" s="1" t="n">
         <v>42434</v>
       </c>
       <c r="O18" t="inlineStr">
@@ -2296,10 +2265,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
+      <c r="A19" t="n">
+        <v>1218</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2353,7 +2320,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O19" t="inlineStr">
@@ -2399,10 +2366,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
+      <c r="A20" t="n">
+        <v>1701</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2454,7 +2419,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N20" s="1" t="n">
         <v>42701</v>
       </c>
       <c r="O20" t="inlineStr">
@@ -2500,10 +2465,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
+      <c r="A21" t="n">
+        <v>1704</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2555,7 +2518,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" s="1" t="n">
         <v>36103</v>
       </c>
       <c r="O21" t="inlineStr">
@@ -2601,10 +2564,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
+      <c r="A22" t="n">
+        <v>1704</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2658,7 +2619,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N22" s="3" t="n">
+      <c r="N22" s="1" t="n">
         <v>41799</v>
       </c>
       <c r="O22" t="inlineStr">
@@ -2704,10 +2665,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
+      <c r="A23" t="n">
+        <v>1705</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2759,7 +2718,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N23" s="3" t="n">
+      <c r="N23" s="1" t="n">
         <v>42810</v>
       </c>
       <c r="O23" t="inlineStr">
@@ -2805,10 +2764,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
+      <c r="A24" t="n">
+        <v>1705</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2862,7 +2819,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N24" s="3" t="n">
+      <c r="N24" s="1" t="n">
         <v>40707</v>
       </c>
       <c r="O24" t="inlineStr">
@@ -2908,10 +2865,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
+      <c r="A25" t="n">
+        <v>1705</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2965,7 +2920,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N25" s="3" t="n">
+      <c r="N25" s="1" t="n">
         <v>43185</v>
       </c>
       <c r="O25" t="inlineStr">
@@ -3011,10 +2966,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
+      <c r="A26" t="n">
+        <v>1705</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3068,7 +3021,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N26" s="3" t="n">
+      <c r="N26" s="1" t="n">
         <v>42811</v>
       </c>
       <c r="O26" t="inlineStr">
@@ -3114,10 +3067,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
+      <c r="A27" t="n">
+        <v>1706</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3171,7 +3122,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="N27" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O27" t="inlineStr">
@@ -3217,10 +3168,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
+      <c r="A28" t="n">
+        <v>1706</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3274,7 +3223,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N28" s="3" t="n">
+      <c r="N28" s="1" t="n">
         <v>42222</v>
       </c>
       <c r="O28" t="inlineStr">
@@ -3320,10 +3269,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A29" t="n">
+        <v>1710</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3377,7 +3324,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="1" t="n">
         <v>37286</v>
       </c>
       <c r="O29" t="inlineStr">
@@ -3423,10 +3370,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A30" t="n">
+        <v>1710</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3480,7 +3425,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N30" s="3" t="n">
+      <c r="N30" s="1" t="n">
         <v>37286</v>
       </c>
       <c r="O30" t="inlineStr">
@@ -3526,10 +3471,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A31" t="n">
+        <v>1710</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3583,7 +3526,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N31" s="3" t="n">
+      <c r="N31" s="1" t="n">
         <v>40290</v>
       </c>
       <c r="O31" t="inlineStr">
@@ -3629,10 +3572,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A32" t="n">
+        <v>1711</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -3686,7 +3627,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N32" s="3" t="n">
+      <c r="N32" s="1" t="n">
         <v>40403</v>
       </c>
       <c r="O32" t="inlineStr">
@@ -3732,10 +3673,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A33" t="n">
+        <v>1714</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3787,7 +3726,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N33" s="3" t="n">
+      <c r="N33" s="1" t="n">
         <v>39926</v>
       </c>
       <c r="O33" t="inlineStr">
@@ -3833,10 +3772,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A34" t="n">
+        <v>1714</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3888,7 +3825,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N34" s="3" t="n">
+      <c r="N34" s="1" t="n">
         <v>43034</v>
       </c>
       <c r="O34" t="inlineStr">
@@ -3934,10 +3871,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A35" t="n">
+        <v>1714</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3989,7 +3924,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N35" s="3" t="n">
+      <c r="N35" s="1" t="n">
         <v>42045</v>
       </c>
       <c r="O35" t="inlineStr">
@@ -4035,10 +3970,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A36" t="n">
+        <v>1714</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4092,7 +4025,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N36" s="3" t="n">
+      <c r="N36" s="1" t="n">
         <v>43705</v>
       </c>
       <c r="O36" t="inlineStr">
@@ -4138,10 +4071,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A37" t="n">
+        <v>1714</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4193,7 +4124,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N37" s="3" t="n">
+      <c r="N37" s="1" t="n">
         <v>42242</v>
       </c>
       <c r="O37" t="inlineStr">
@@ -4239,10 +4170,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A38" t="n">
+        <v>1714</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4294,7 +4223,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N38" s="3" t="n">
+      <c r="N38" s="1" t="n">
         <v>42587</v>
       </c>
       <c r="O38" t="inlineStr">
@@ -4340,10 +4269,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A39" t="n">
+        <v>1716</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4395,7 +4322,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N39" s="3" t="n">
+      <c r="N39" s="1" t="n">
         <v>43003</v>
       </c>
       <c r="O39" t="inlineStr">
@@ -4441,10 +4368,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>1720</t>
-        </is>
+      <c r="A40" t="n">
+        <v>1720</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -4498,7 +4423,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N40" s="3" t="n">
+      <c r="N40" s="1" t="n">
         <v>40928</v>
       </c>
       <c r="O40" t="inlineStr">
@@ -4544,10 +4469,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A41" t="n">
+        <v>1722</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -4601,7 +4524,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N41" s="3" t="n">
+      <c r="N41" s="1" t="n">
         <v>43073</v>
       </c>
       <c r="O41" t="inlineStr">
@@ -4647,10 +4570,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A42" t="n">
+        <v>1729</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -4704,7 +4625,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N42" s="3" t="n">
+      <c r="N42" s="1" t="n">
         <v>42588</v>
       </c>
       <c r="O42" t="inlineStr">
@@ -4750,10 +4671,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>1735</t>
-        </is>
+      <c r="A43" t="n">
+        <v>1735</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -4807,7 +4726,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N43" s="3" t="n">
+      <c r="N43" s="1" t="n">
         <v>42543</v>
       </c>
       <c r="O43" t="inlineStr">
@@ -4853,10 +4772,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+      <c r="A44" t="n">
+        <v>1803</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -4908,7 +4825,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N44" s="3" t="n">
+      <c r="N44" s="1" t="n">
         <v>40213</v>
       </c>
       <c r="O44" t="inlineStr">
@@ -4954,10 +4871,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
+      <c r="A45" t="n">
+        <v>1805</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -5009,7 +4924,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N45" s="3" t="n">
+      <c r="N45" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O45" t="inlineStr">
@@ -5055,10 +4970,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A46" t="n">
+        <v>1813</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -5112,7 +5025,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N46" s="3" t="n">
+      <c r="N46" s="1" t="n">
         <v>43166</v>
       </c>
       <c r="O46" t="inlineStr">
@@ -5158,10 +5071,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
+      <c r="A47" t="n">
+        <v>1815</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5215,7 +5126,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N47" s="3" t="n">
+      <c r="N47" s="1" t="n">
         <v>39799</v>
       </c>
       <c r="O47" t="inlineStr">
@@ -5261,10 +5172,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A48" t="n">
+        <v>1818</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -5318,7 +5227,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N48" s="3" t="n">
+      <c r="N48" s="1" t="n">
         <v>42132</v>
       </c>
       <c r="O48" t="inlineStr">
@@ -5364,10 +5273,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A49" t="n">
+        <v>1818</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -5421,7 +5328,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N49" s="3" t="n">
+      <c r="N49" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O49" t="inlineStr">
@@ -5467,10 +5374,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A50" t="n">
+        <v>1823</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -5524,7 +5429,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N50" s="3" t="n">
+      <c r="N50" s="1" t="n">
         <v>40589</v>
       </c>
       <c r="O50" t="inlineStr">
@@ -5570,10 +5475,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="A51" t="n">
+        <v>1826</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -5627,7 +5530,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N51" s="3" t="n">
+      <c r="N51" s="1" t="n">
         <v>42137</v>
       </c>
       <c r="O51" t="inlineStr">
@@ -5673,10 +5576,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A52" t="n">
+        <v>1828</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -5720,7 +5621,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N52" s="3" t="n">
+      <c r="N52" s="1" t="n">
         <v>44959</v>
       </c>
       <c r="O52" t="inlineStr">
@@ -5766,10 +5667,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
+      <c r="A53" t="n">
+        <v>1830</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -5823,7 +5722,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N53" s="3" t="n">
+      <c r="N53" s="1" t="n">
         <v>42791</v>
       </c>
       <c r="O53" t="inlineStr">
@@ -5869,10 +5768,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A54" t="n">
+        <v>2102</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -5926,7 +5823,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N54" s="3" t="n">
+      <c r="N54" s="1" t="n">
         <v>36790</v>
       </c>
       <c r="O54" t="inlineStr">
@@ -5972,10 +5869,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A55" t="n">
+        <v>2102</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -6029,7 +5924,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N55" s="3" t="n">
+      <c r="N55" s="1" t="n">
         <v>36790</v>
       </c>
       <c r="O55" t="inlineStr">
@@ -6075,10 +5970,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A56" t="n">
+        <v>2102</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6132,7 +6025,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N56" s="3" t="n">
+      <c r="N56" s="1" t="n">
         <v>43326</v>
       </c>
       <c r="O56" t="inlineStr">
@@ -6178,10 +6071,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+      <c r="A57" t="n">
+        <v>2106</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -6235,7 +6126,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N57" s="3" t="n">
+      <c r="N57" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O57" t="inlineStr">
@@ -6281,10 +6172,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
+      <c r="A58" t="n">
+        <v>2702</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -6336,7 +6225,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N58" s="3" t="n">
+      <c r="N58" s="1" t="n">
         <v>36914</v>
       </c>
       <c r="O58" t="inlineStr">
@@ -6382,10 +6271,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2721</t>
-        </is>
+      <c r="A59" t="n">
+        <v>2721</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -6439,7 +6326,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N59" s="3" t="n">
+      <c r="N59" s="1" t="n">
         <v>43341</v>
       </c>
       <c r="O59" t="inlineStr">
@@ -6485,10 +6372,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2812</t>
-        </is>
+      <c r="A60" t="n">
+        <v>2812</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -6542,7 +6427,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N60" s="3" t="n">
+      <c r="N60" s="1" t="n">
         <v>42105</v>
       </c>
       <c r="O60" t="inlineStr">
@@ -6588,10 +6473,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2831</t>
-        </is>
+      <c r="A61" t="n">
+        <v>2831</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -6643,7 +6526,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N61" s="3" t="n">
+      <c r="N61" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="O61" t="inlineStr">
@@ -6689,10 +6572,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2831</t>
-        </is>
+      <c r="A62" t="n">
+        <v>2831</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -6744,7 +6625,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N62" s="3" t="n">
+      <c r="N62" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="O62" t="inlineStr">
@@ -6790,10 +6671,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A63" t="n">
+        <v>2832</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -6845,7 +6724,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N63" s="3" t="n">
+      <c r="N63" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="O63" t="inlineStr">
@@ -6891,10 +6770,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
+      <c r="A64" t="n">
+        <v>2833</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -6948,7 +6825,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N64" s="3" t="n">
+      <c r="N64" s="1" t="n">
         <v>42192</v>
       </c>
       <c r="O64" t="inlineStr">
@@ -6994,10 +6871,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>9930</t>
-        </is>
+      <c r="A65" t="n">
+        <v>9930</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -7051,7 +6926,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N65" s="3" t="n">
+      <c r="N65" s="1" t="n">
         <v>44096</v>
       </c>
       <c r="O65" t="inlineStr">
@@ -7097,10 +6972,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>9930</t>
-        </is>
+      <c r="A66" t="n">
+        <v>9930</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -7154,7 +7027,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N66" s="3" t="n">
+      <c r="N66" s="1" t="n">
         <v>44092</v>
       </c>
       <c r="O66" t="inlineStr">
